--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511F648D-A986-472F-B5C7-2DAD7C6C2B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C787A9-D13F-4960-914E-63B54F38CCFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="0" windowWidth="15120" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14910" yWindow="0" windowWidth="15405" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="70">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -324,6 +324,22 @@
     <rPh sb="0" eb="2">
       <t>ヒトリ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5389,7 +5405,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H433"/>
+  <dimension ref="A2:H444"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9948,7 +9964,7 @@
     </row>
     <row r="386" spans="1:3">
       <c r="A386">
-        <f t="shared" ref="A386:A433" si="13">A385+1</f>
+        <f t="shared" ref="A386:A444" si="13">A385+1</f>
         <v>103</v>
       </c>
       <c r="B386" t="s">
@@ -10482,6 +10498,9 @@
       <c r="B430" t="s">
         <v>9</v>
       </c>
+      <c r="C430">
+        <v>1</v>
+      </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431">
@@ -10491,6 +10510,9 @@
       <c r="B431" t="s">
         <v>8</v>
       </c>
+      <c r="C431">
+        <v>1</v>
+      </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432">
@@ -10500,14 +10522,145 @@
       <c r="B432" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="433" spans="1:2">
+      <c r="C432">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3">
       <c r="A433">
         <f t="shared" si="13"/>
         <v>150</v>
       </c>
       <c r="B433" t="s">
         <v>8</v>
+      </c>
+      <c r="C433">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3">
+      <c r="A434">
+        <v>101</v>
+      </c>
+      <c r="B434" t="s">
+        <v>66</v>
+      </c>
+      <c r="C434">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3">
+      <c r="A435">
+        <f t="shared" si="13"/>
+        <v>102</v>
+      </c>
+      <c r="B435" t="s">
+        <v>66</v>
+      </c>
+      <c r="C435">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3">
+      <c r="A436">
+        <f t="shared" si="13"/>
+        <v>103</v>
+      </c>
+      <c r="B436" t="s">
+        <v>67</v>
+      </c>
+      <c r="C436">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3">
+      <c r="A437">
+        <f t="shared" si="13"/>
+        <v>104</v>
+      </c>
+      <c r="B437" t="s">
+        <v>67</v>
+      </c>
+      <c r="C437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3">
+      <c r="A438">
+        <f t="shared" si="13"/>
+        <v>105</v>
+      </c>
+      <c r="B438" t="s">
+        <v>68</v>
+      </c>
+      <c r="C438">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3">
+      <c r="A439">
+        <f t="shared" si="13"/>
+        <v>106</v>
+      </c>
+      <c r="B439" t="s">
+        <v>68</v>
+      </c>
+      <c r="C439">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3">
+      <c r="A440">
+        <f t="shared" si="13"/>
+        <v>107</v>
+      </c>
+      <c r="B440" t="s">
+        <v>67</v>
+      </c>
+      <c r="C440">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3">
+      <c r="A441">
+        <f t="shared" si="13"/>
+        <v>108</v>
+      </c>
+      <c r="B441" t="s">
+        <v>66</v>
+      </c>
+      <c r="C441">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3">
+      <c r="A442">
+        <f t="shared" si="13"/>
+        <v>109</v>
+      </c>
+      <c r="B442" t="s">
+        <v>69</v>
+      </c>
+      <c r="C442">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3">
+      <c r="A443">
+        <f t="shared" si="13"/>
+        <v>110</v>
+      </c>
+      <c r="B443" t="s">
+        <v>67</v>
+      </c>
+      <c r="C443">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3">
+      <c r="A444">
+        <f t="shared" si="13"/>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/1st.xlsx
+++ b/l_r/1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C787A9-D13F-4960-914E-63B54F38CCFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBE703D-3540-4C27-9660-1819EFA18F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14910" yWindow="0" windowWidth="15405" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1005" yWindow="0" windowWidth="12525" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -340,6 +340,22 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5405,7 +5421,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H444"/>
+  <dimension ref="A2:H453"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9964,7 +9980,7 @@
     </row>
     <row r="386" spans="1:3">
       <c r="A386">
-        <f t="shared" ref="A386:A444" si="13">A385+1</f>
+        <f t="shared" ref="A386:A449" si="13">A385+1</f>
         <v>103</v>
       </c>
       <c r="B386" t="s">
@@ -10661,6 +10677,120 @@
       <c r="A444">
         <f t="shared" si="13"/>
         <v>111</v>
+      </c>
+      <c r="B444" t="s">
+        <v>70</v>
+      </c>
+      <c r="C444">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3">
+      <c r="A445">
+        <f t="shared" si="13"/>
+        <v>112</v>
+      </c>
+      <c r="B445" t="s">
+        <v>71</v>
+      </c>
+      <c r="C445">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3">
+      <c r="A446">
+        <f t="shared" si="13"/>
+        <v>113</v>
+      </c>
+      <c r="B446" t="s">
+        <v>72</v>
+      </c>
+      <c r="C446">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3">
+      <c r="A447">
+        <f t="shared" si="13"/>
+        <v>114</v>
+      </c>
+      <c r="B447" t="s">
+        <v>70</v>
+      </c>
+      <c r="C447">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3">
+      <c r="A448">
+        <f t="shared" si="13"/>
+        <v>115</v>
+      </c>
+      <c r="B448" t="s">
+        <v>72</v>
+      </c>
+      <c r="C448">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3">
+      <c r="A449">
+        <f t="shared" si="13"/>
+        <v>116</v>
+      </c>
+      <c r="B449" t="s">
+        <v>71</v>
+      </c>
+      <c r="C449">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3">
+      <c r="A450">
+        <f t="shared" ref="A450:A453" si="14">A449+1</f>
+        <v>117</v>
+      </c>
+      <c r="B450" t="s">
+        <v>73</v>
+      </c>
+      <c r="C450">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3">
+      <c r="A451">
+        <f t="shared" si="14"/>
+        <v>118</v>
+      </c>
+      <c r="B451" t="s">
+        <v>70</v>
+      </c>
+      <c r="C451">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3">
+      <c r="A452">
+        <f t="shared" si="14"/>
+        <v>119</v>
+      </c>
+      <c r="B452" t="s">
+        <v>70</v>
+      </c>
+      <c r="C452">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3">
+      <c r="A453">
+        <f t="shared" si="14"/>
+        <v>120</v>
+      </c>
+      <c r="B453" t="s">
+        <v>71</v>
+      </c>
+      <c r="C453">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
